--- a/data/xlsx/lfmeab--merchandising-for-footwear-and-leather-goods-sector.xlsx
+++ b/data/xlsx/lfmeab--merchandising-for-footwear-and-leather-goods-sector.xlsx
@@ -647,7 +647,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -669,7 +671,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -691,7 +695,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -713,7 +719,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -733,7 +741,9 @@
         </is>
       </c>
       <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -759,7 +769,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -785,7 +797,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -807,7 +821,9 @@
       <c r="C23" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -829,7 +845,9 @@
       <c r="C24" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -851,7 +869,9 @@
       <c r="C25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -873,7 +893,9 @@
       <c r="C26" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -895,7 +917,9 @@
       <c r="C27" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -917,7 +941,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -943,7 +969,9 @@
       <c r="C29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>3</v>
       </c>
@@ -965,7 +993,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -987,7 +1017,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -1009,7 +1041,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>4</v>
       </c>
@@ -1031,7 +1065,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>4</v>
       </c>
